--- a/media_material/admin/students导入模板.xlsx
+++ b/media_material/admin/students导入模板.xlsx
@@ -29,13 +29,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
   <si>
-    <t>student_id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>teacher_name</t>
+    <t>student_username</t>
+  </si>
+  <si>
+    <t>student_name</t>
+  </si>
+  <si>
+    <t>teacher_username</t>
   </si>
   <si>
     <t>year</t>
@@ -59,7 +59,7 @@
     <t>class_begin_time</t>
   </si>
   <si>
-    <t>end_time</t>
+    <t>class_end_time</t>
   </si>
   <si>
     <t>Tim</t>
